--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10911"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucifer/vscode_Luci_scripts/HBCD-DOCS/2.1-dev/hbcd-docs/docs/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB98ECB7-13A0-3A47-A3E6-6A1A886010F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="🤩 public data release"/>
+    <sheet name="🤩 public data release" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="224">
   <si>
     <t>Name</t>
   </si>
@@ -388,15 +394,6 @@
     <t>Demographics V6 Adult</t>
   </si>
   <si>
-    <t>Addition of V6 Adult</t>
-  </si>
-  <si>
-    <t>Demographics V6 Child</t>
-  </si>
-  <si>
-    <t>Addition of V6 Child</t>
-  </si>
-  <si>
     <t>Geocoded Linkage from Home and Work Addresses</t>
   </si>
   <si>
@@ -631,7 +628,7 @@
     <t>dMRI metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">`LargeDelta` and `SmallDelta` in the sidecars currently are set to vendor-specific values (which aren't always correct because the models have their own values) and ﻿will be updated to reflect accurate values.﻿ ﻿</t>
+    <t>`LargeDelta` and `SmallDelta` in the sidecars currently are set to vendor-specific values (which aren't always correct because the models have their own values) and ﻿will be updated to reflect accurate values.﻿ ﻿</t>
   </si>
   <si>
     <t>Add tabulated MR raw data QC</t>
@@ -692,12 +689,15 @@
   </si>
   <si>
     <t>Addition of V06</t>
+  </si>
+  <si>
+    <t>Addition of V6 Adult and V6 Child Demographics</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
@@ -724,7 +724,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -738,102 +738,102 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFd6d6d6"/>
+        <fgColor rgb="FFD6D6D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFc4c4c4"/>
+        <fgColor rgb="FFC4C4C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66ccff"/>
+        <fgColor rgb="FF66CCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFbb3354"/>
+        <fgColor rgb="FFBB3354"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9d99b9"/>
+        <fgColor rgb="FF9D99B9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00c875"/>
+        <fgColor rgb="FF00C875"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9cd326"/>
+        <fgColor rgb="FF9CD326"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffadad"/>
+        <fgColor rgb="FFFFADAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF007eb5"/>
+        <fgColor rgb="FF007EB5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFfdab3d"/>
+        <fgColor rgb="FFFDAB3D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFdf2f4a"/>
+        <fgColor rgb="FFDF2F4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFff007f"/>
+        <fgColor rgb="FFFF007F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF784bd1"/>
+        <fgColor rgb="FF784BD1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9d50dd"/>
+        <fgColor rgb="FF9D50DD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffcb00"/>
+        <fgColor rgb="FFFFCB00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF563e3e"/>
+        <fgColor rgb="FF563E3E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFcab641"/>
+        <fgColor rgb="FFCAB641"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFff7575"/>
+        <fgColor rgb="FFFF7575"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF037f4c"/>
+        <fgColor rgb="FF037F4C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFff5ac4"/>
+        <fgColor rgb="FFFF5AC4"/>
       </patternFill>
     </fill>
   </fills>
@@ -847,16 +847,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -871,116 +871,103 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="15" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="16" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="17" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="18" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="19" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="20" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="21" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -991,10 +978,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1032,71 +1019,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1124,7 +1111,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1147,11 +1134,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1160,13 +1147,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1176,7 +1163,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1185,7 +1172,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1194,7 +1181,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1202,10 +1189,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1270,27 +1257,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K68"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="31" width="37.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="32" width="3.5764285714285715" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="33" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="31" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="31" width="9.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="31" width="46.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="31" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="31" width="29.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="31" width="31.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="31" width="150.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="31" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="150" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1325,7 +1312,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1358,7 +1345,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1391,7 +1378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>24</v>
       </c>
@@ -1424,7 +1411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -1457,7 +1444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
@@ -1490,7 +1477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -1523,7 +1510,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="26.75">
+    <row r="8" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>41</v>
       </c>
@@ -1556,7 +1543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="26.75">
+    <row r="9" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>44</v>
       </c>
@@ -1589,7 +1576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="26.75">
+    <row r="10" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>49</v>
       </c>
@@ -1622,7 +1609,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="26.75">
+    <row r="11" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>52</v>
       </c>
@@ -1655,7 +1642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="26.75">
+    <row r="12" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>55</v>
       </c>
@@ -1688,7 +1675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="26.75">
+    <row r="13" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>57</v>
       </c>
@@ -1721,7 +1708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="26.75">
+    <row r="14" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>61</v>
       </c>
@@ -1754,7 +1741,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="26.75">
+    <row r="15" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
@@ -1785,7 +1772,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="26.75">
+    <row r="16" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>68</v>
       </c>
@@ -1818,7 +1805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="26.75">
+    <row r="17" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>72</v>
       </c>
@@ -1849,7 +1836,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="26.75">
+    <row r="18" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>79</v>
       </c>
@@ -1882,7 +1869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="26.75">
+    <row r="19" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>81</v>
       </c>
@@ -1915,7 +1902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="26.75">
+    <row r="20" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>85</v>
       </c>
@@ -1948,7 +1935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="26.75">
+    <row r="21" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>88</v>
       </c>
@@ -1981,7 +1968,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="26.75">
+    <row r="22" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>91</v>
       </c>
@@ -2014,7 +2001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="26.75">
+    <row r="23" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>93</v>
       </c>
@@ -2047,7 +2034,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="26.75">
+    <row r="24" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>96</v>
       </c>
@@ -2080,7 +2067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="26.75">
+    <row r="25" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>98</v>
       </c>
@@ -2113,7 +2100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="26.75">
+    <row r="26" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>101</v>
       </c>
@@ -2146,7 +2133,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="26.75">
+    <row r="27" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>103</v>
       </c>
@@ -2179,7 +2166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="26.75">
+    <row r="28" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>107</v>
       </c>
@@ -2212,7 +2199,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="26.75">
+    <row r="29" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>111</v>
       </c>
@@ -2245,7 +2232,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="26.75">
+    <row r="30" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>114</v>
       </c>
@@ -2278,7 +2265,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="26.75">
+    <row r="31" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>116</v>
       </c>
@@ -2311,7 +2298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="26.75">
+    <row r="32" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>120</v>
       </c>
@@ -2344,7 +2331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="26.75">
+    <row r="33" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>123</v>
       </c>
@@ -2371,25 +2358,25 @@
         <v>99</v>
       </c>
       <c r="J33" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="K33" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="26.75">
-      <c r="A34" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="B34" s="5">
         <v>3</v>
       </c>
       <c r="C34" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D34" s="7"/>
-      <c r="E34" s="23" t="s">
-        <v>117</v>
+      <c r="E34" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>69</v>
@@ -2401,7 +2388,7 @@
         <v>15</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>126</v>
@@ -2410,7 +2397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="26.75">
+    <row r="35" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>127</v>
       </c>
@@ -2418,11 +2405,11 @@
         <v>3</v>
       </c>
       <c r="C35" s="6">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D35" s="7"/>
-      <c r="E35" s="19" t="s">
-        <v>58</v>
+      <c r="E35" s="23" t="s">
+        <v>117</v>
       </c>
       <c r="F35" s="21" t="s">
         <v>69</v>
@@ -2443,7 +2430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="26.75">
+    <row r="36" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>130</v>
       </c>
@@ -2454,11 +2441,11 @@
         <v>30</v>
       </c>
       <c r="D36" s="7"/>
-      <c r="E36" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>69</v>
+      <c r="E36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>14</v>
@@ -2476,7 +2463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="26.75">
+    <row r="37" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>133</v>
       </c>
@@ -2487,8 +2474,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="7"/>
-      <c r="E37" s="8" t="s">
-        <v>12</v>
+      <c r="E37" s="23" t="s">
+        <v>117</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>21</v>
@@ -2509,7 +2496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="26.75">
+    <row r="38" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>136</v>
       </c>
@@ -2523,8 +2510,8 @@
       <c r="E38" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="F38" s="8" t="s">
-        <v>21</v>
+      <c r="F38" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>14</v>
@@ -2533,31 +2520,31 @@
         <v>15</v>
       </c>
       <c r="I38" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="J38" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="J38" s="12" t="s">
+      <c r="K38" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K38" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="26.75">
-      <c r="A39" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="B39" s="5">
         <v>3</v>
       </c>
       <c r="C39" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D39" s="7"/>
-      <c r="E39" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>13</v>
+      <c r="E39" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>14</v>
@@ -2575,7 +2562,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="26.75">
+    <row r="40" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>141</v>
       </c>
@@ -2586,14 +2573,14 @@
         <v>30.1</v>
       </c>
       <c r="D40" s="7"/>
-      <c r="E40" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>14</v>
+      <c r="E40" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>15</v>
@@ -2608,7 +2595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="26.75">
+    <row r="41" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>144</v>
       </c>
@@ -2619,11 +2606,11 @@
         <v>30.1</v>
       </c>
       <c r="D41" s="7"/>
-      <c r="E41" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>104</v>
+      <c r="E41" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>31</v>
@@ -2641,7 +2628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="26.75">
+    <row r="42" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>147</v>
       </c>
@@ -2649,14 +2636,14 @@
         <v>3</v>
       </c>
       <c r="C42" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D42" s="7"/>
-      <c r="E42" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>38</v>
+      <c r="E42" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>31</v>
@@ -2674,7 +2661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="26.75">
+    <row r="43" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>150</v>
       </c>
@@ -2682,14 +2669,14 @@
         <v>3</v>
       </c>
       <c r="C43" s="6">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D43" s="7"/>
-      <c r="E43" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="23" t="s">
-        <v>104</v>
+      <c r="E43" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>31</v>
@@ -2698,31 +2685,31 @@
         <v>15</v>
       </c>
       <c r="I43" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J43" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="K43" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K43" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="26.75">
-      <c r="A44" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="B44" s="5">
         <v>3</v>
       </c>
       <c r="C44" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="17" t="s">
-        <v>38</v>
+      <c r="F44" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>31</v>
@@ -2731,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="J44" s="12" t="s">
         <v>154</v>
@@ -2740,7 +2727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="26.75">
+    <row r="45" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>155</v>
       </c>
@@ -2751,14 +2738,14 @@
         <v>30.1</v>
       </c>
       <c r="D45" s="7"/>
-      <c r="E45" s="9" t="s">
-        <v>30</v>
+      <c r="E45" s="16" t="s">
+        <v>45</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G45" s="16" t="s">
-        <v>31</v>
+      <c r="G45" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>15</v>
@@ -2773,7 +2760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="26.75">
+    <row r="46" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>158</v>
       </c>
@@ -2781,14 +2768,14 @@
         <v>3</v>
       </c>
       <c r="C46" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F46" s="15" t="s">
-        <v>26</v>
+      <c r="F46" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>14</v>
@@ -2806,7 +2793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="26.75">
+    <row r="47" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>161</v>
       </c>
@@ -2835,109 +2822,102 @@
       <c r="J47" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="K47" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="26.75">
+      <c r="K47" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" s="20"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B48" s="5">
-        <v>3</v>
-      </c>
-      <c r="C48" s="6">
-        <v>30.2</v>
-      </c>
-      <c r="D48" s="7"/>
-      <c r="E48" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="J48" s="12" t="s">
-        <v>166</v>
-      </c>
+      <c r="H48" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
       <c r="K48" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="26.75">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B49" s="25"/>
-      <c r="C49" s="20"/>
+      <c r="B49" s="5">
+        <v>3</v>
+      </c>
+      <c r="C49" s="6">
+        <v>30.1</v>
+      </c>
       <c r="D49" s="7"/>
-      <c r="E49" s="18" t="s">
-        <v>169</v>
+      <c r="E49" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
       <c r="K49" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="26.75">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" s="20"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="J50" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B50" s="5">
-        <v>3</v>
-      </c>
-      <c r="C50" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="D50" s="7"/>
-      <c r="E50" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="26.75">
+      <c r="K50" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B51" s="25"/>
       <c r="C51" s="20"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>13</v>
+      <c r="E51" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>14</v>
@@ -2955,21 +2935,20 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="26.75">
+    <row r="52" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B52" s="25"/>
       <c r="C52" s="20"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F52" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>14</v>
+      <c r="F52" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H52" s="11" t="s">
         <v>15</v>
@@ -2984,24 +2963,23 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="26.75">
+    <row r="53" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B53" s="25"/>
       <c r="C53" s="20"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F53" s="23" t="s">
-        <v>104</v>
+      <c r="F53" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H53" s="11" t="s">
-        <v>15</v>
+      <c r="H53" s="21" t="s">
+        <v>76</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>179</v>
@@ -3009,28 +2987,27 @@
       <c r="J53" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="K53" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="26.75">
+      <c r="K53" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B54" s="25"/>
       <c r="C54" s="20"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F54" s="15" t="s">
-        <v>26</v>
+      <c r="F54" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H54" s="21" t="s">
-        <v>76</v>
+      <c r="H54" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="I54" s="12" t="s">
         <v>182</v>
@@ -3038,25 +3015,24 @@
       <c r="J54" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="K54" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="26.75">
+      <c r="K54" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B55" s="25"/>
       <c r="C55" s="20"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>31</v>
+      <c r="E55" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H55" s="11" t="s">
         <v>15</v>
@@ -3071,21 +3047,20 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="26.75">
+    <row r="56" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B56" s="25"/>
       <c r="C56" s="20"/>
       <c r="D56" s="7"/>
-      <c r="E56" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>14</v>
+      <c r="E56" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H56" s="11" t="s">
         <v>15</v>
@@ -3100,11 +3075,10 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="26.75">
+    <row r="57" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B57" s="25"/>
       <c r="C57" s="20"/>
       <c r="D57" s="7"/>
       <c r="E57" s="15" t="s">
@@ -3120,27 +3094,26 @@
         <v>15</v>
       </c>
       <c r="I57" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="J57" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="K57" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="K57" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="26.75">
-      <c r="A58" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B58" s="25"/>
       <c r="C58" s="20"/>
       <c r="D58" s="7"/>
-      <c r="E58" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F58" s="16" t="s">
-        <v>74</v>
+      <c r="E58" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G58" s="16" t="s">
         <v>31</v>
@@ -3149,88 +3122,85 @@
         <v>15</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="J58" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="K58" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="26.75">
-      <c r="A59" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B59" s="25"/>
       <c r="C59" s="20"/>
       <c r="D59" s="7"/>
-      <c r="E59" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>31</v>
+      <c r="E59" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G59" s="26" t="s">
+        <v>195</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="K59" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="26.75">
+      <c r="K59" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B60" s="25"/>
       <c r="C60" s="20"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F60" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="G60" s="26" t="s">
+      <c r="F60" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="12" t="s">
         <v>198</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="J60" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="K60" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="26.75">
+      <c r="K60" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B61" s="25"/>
       <c r="C61" s="20"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F61" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>14</v>
+      <c r="F61" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>15</v>
@@ -3245,21 +3215,20 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="26.75">
+    <row r="62" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B62" s="25"/>
       <c r="C62" s="20"/>
       <c r="D62" s="7"/>
-      <c r="E62" s="7" t="s">
-        <v>73</v>
+      <c r="E62" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G62" s="16" t="s">
-        <v>31</v>
+      <c r="G62" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H62" s="11" t="s">
         <v>15</v>
@@ -3274,38 +3243,44 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="26.75">
+    <row r="63" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B63" s="25"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>46</v>
+      <c r="B63" s="5">
+        <v>3</v>
+      </c>
+      <c r="C63" s="6">
+        <v>30</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" s="27" t="s">
+        <v>208</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H63" s="11" t="s">
-        <v>15</v>
+      <c r="H63" s="28" t="s">
+        <v>209</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="26.75">
+    <row r="64" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B64" s="5">
         <v>3</v>
@@ -3314,54 +3289,54 @@
         <v>30</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F64" s="27" t="s">
-        <v>211</v>
+      <c r="F64" s="24" t="s">
+        <v>108</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="I64" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="I64" s="12" t="s">
+      <c r="J64" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="J64" s="12" t="s">
+      <c r="K64" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="K64" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="26.75">
-      <c r="A65" s="4" t="s">
-        <v>215</v>
-      </c>
       <c r="B65" s="5">
         <v>3</v>
       </c>
       <c r="C65" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F65" s="24" t="s">
-        <v>108</v>
+      <c r="F65" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H65" s="28" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>215</v>
@@ -3373,7 +3348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="26.75">
+    <row r="66" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>217</v>
       </c>
@@ -3381,22 +3356,22 @@
         <v>3</v>
       </c>
       <c r="C66" s="6">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F66" s="18" t="s">
-        <v>46</v>
+      <c r="F66" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="28" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>218</v>
@@ -3408,7 +3383,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="26.75">
+    <row r="67" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>220</v>
       </c>
@@ -3419,19 +3394,19 @@
         <v>30</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F67" s="23" t="s">
-        <v>104</v>
+      <c r="F67" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H67" s="28" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I67" s="12" t="s">
         <v>221</v>
@@ -3443,54 +3418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="26.75">
-      <c r="A68" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B68" s="5">
-        <v>3</v>
-      </c>
-      <c r="C68" s="6">
-        <v>30</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="J68" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="K68" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="26.75">
-      <c r="A69" s="29"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-    </row>
+    <row r="68" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucifer/vscode_Luci_scripts/HBCD-DOCS/2.1-dev/hbcd-docs/docs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB98ECB7-13A0-3A47-A3E6-6A1A886010F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A788107-24C6-994B-B1EF-5C12225B8D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="221">
   <si>
     <t>Name</t>
   </si>
@@ -133,16 +133,7 @@
     <t>Pro-rated scoring for `mh_cg_mapdb__tod` not yet implemented; N=16 participants missing scores.</t>
   </si>
   <si>
-    <t>[DATA REQUEST] - static and dynamic tables</t>
-  </si>
-  <si>
     <t>Demographics</t>
-  </si>
-  <si>
-    <t>Static &amp; Dynamic Tables</t>
-  </si>
-  <si>
-    <t>The Demographics domain includes 2 tables with derived information grouped into visit-specific data ([Visit Info](https://docs.hbcdstudy.org/latest/instruments/demo/visitinfo/)) and general demographics ([Basic Demographics](https://docs.hbcdstudy.org/latest/instruments/demo/basicdemo/)). In a future release, these tables will be restructured to instead organize variables as either longitudinal (dynamic measures that change over time) or global (static measures, such as sex assigned at birth and race/ethnicity).</t>
   </si>
   <si>
     <t>[DATA ERROR]- ecPROMIS child-caregiver infant</t>
@@ -1261,7 +1252,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -1477,9 +1468,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5">
         <v>3</v>
@@ -1488,14 +1479,14 @@
         <v>30</v>
       </c>
       <c r="D7" s="7"/>
-      <c r="E7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>14</v>
+      <c r="E7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>15</v>
@@ -1521,23 +1512,23 @@
         <v>30</v>
       </c>
       <c r="D8" s="7"/>
-      <c r="E8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>31</v>
+      <c r="E8" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>18</v>
@@ -1545,7 +1536,7 @@
     </row>
     <row r="9" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5">
         <v>3</v>
@@ -1554,14 +1545,14 @@
         <v>30</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>14</v>
+      <c r="E9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>15</v>
@@ -1584,14 +1575,14 @@
         <v>3</v>
       </c>
       <c r="C10" s="6">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>21</v>
+      <c r="E10" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>31</v>
@@ -1617,14 +1608,14 @@
         <v>3</v>
       </c>
       <c r="C11" s="6">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>26</v>
+      <c r="E11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>31</v>
@@ -1633,10 +1624,10 @@
         <v>15</v>
       </c>
       <c r="I11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>18</v>
@@ -1644,7 +1635,7 @@
     </row>
     <row r="12" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>3</v>
@@ -1653,11 +1644,11 @@
         <v>30.1</v>
       </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>13</v>
+      <c r="E12" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>31</v>
@@ -1666,10 +1657,10 @@
         <v>15</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>18</v>
@@ -1677,20 +1668,20 @@
     </row>
     <row r="13" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="5">
         <v>3</v>
       </c>
       <c r="C13" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>38</v>
+      <c r="E13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>31</v>
@@ -1715,15 +1706,13 @@
       <c r="B14" s="5">
         <v>3</v>
       </c>
-      <c r="C14" s="6">
-        <v>30.2</v>
-      </c>
+      <c r="C14" s="20"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>26</v>
+      <c r="E14" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>31</v>
@@ -1732,10 +1721,10 @@
         <v>15</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>18</v>
@@ -1743,18 +1732,20 @@
     </row>
     <row r="15" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="5">
         <v>3</v>
       </c>
-      <c r="C15" s="20"/>
+      <c r="C15" s="6">
+        <v>30.1</v>
+      </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>38</v>
+      <c r="E15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>31</v>
@@ -1763,10 +1754,10 @@
         <v>15</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>18</v>
@@ -1774,40 +1765,38 @@
     </row>
     <row r="16" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5">
         <v>3</v>
       </c>
       <c r="C16" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>15</v>
+      <c r="E16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>18</v>
+        <v>74</v>
+      </c>
+      <c r="J16" s="12"/>
+      <c r="K16" s="17" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B17" s="5">
         <v>3</v>
@@ -1817,28 +1806,30 @@
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="I17" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="17" t="s">
-        <v>78</v>
+      <c r="K17" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>3</v>
@@ -1847,11 +1838,11 @@
         <v>30.2</v>
       </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>13</v>
+      <c r="E18" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>79</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>31</v>
@@ -1860,10 +1851,10 @@
         <v>15</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>18</v>
@@ -1871,23 +1862,23 @@
     </row>
     <row r="19" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="5">
         <v>3</v>
       </c>
       <c r="C19" s="6">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>31</v>
+      <c r="E19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H19" s="11" t="s">
         <v>15</v>
@@ -1913,11 +1904,11 @@
         <v>30.1</v>
       </c>
       <c r="D20" s="7"/>
-      <c r="E20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>74</v>
+      <c r="E20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>79</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>14</v>
@@ -1943,14 +1934,14 @@
         <v>3</v>
       </c>
       <c r="C21" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D21" s="7"/>
-      <c r="E21" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>82</v>
+      <c r="E21" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>14</v>
@@ -1959,10 +1950,10 @@
         <v>15</v>
       </c>
       <c r="I21" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>90</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>18</v>
@@ -1970,29 +1961,29 @@
     </row>
     <row r="22" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="5">
+        <v>3</v>
+      </c>
+      <c r="C22" s="6">
+        <v>30</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="B22" s="5">
-        <v>3</v>
-      </c>
-      <c r="C22" s="6">
-        <v>30.2</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>22</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>92</v>
@@ -2009,14 +2000,14 @@
         <v>3</v>
       </c>
       <c r="C23" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D23" s="7"/>
-      <c r="E23" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>74</v>
+      <c r="E23" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>31</v>
@@ -2025,10 +2016,10 @@
         <v>15</v>
       </c>
       <c r="I23" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="12" t="s">
         <v>94</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>95</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>18</v>
@@ -2036,7 +2027,7 @@
     </row>
     <row r="24" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>3</v>
@@ -2045,20 +2036,20 @@
         <v>30.1</v>
       </c>
       <c r="D24" s="7"/>
-      <c r="E24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>31</v>
+      <c r="E24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="J24" s="12" t="s">
         <v>97</v>
@@ -2075,26 +2066,26 @@
         <v>3</v>
       </c>
       <c r="C25" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D25" s="7"/>
-      <c r="E25" s="8" t="s">
-        <v>12</v>
+      <c r="E25" s="16" t="s">
+        <v>42</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>14</v>
+        <v>66</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J25" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>100</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>18</v>
@@ -2102,7 +2093,7 @@
     </row>
     <row r="26" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>3</v>
@@ -2111,11 +2102,11 @@
         <v>30.2</v>
       </c>
       <c r="D26" s="7"/>
-      <c r="E26" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>69</v>
+      <c r="E26" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>101</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>31</v>
@@ -2124,10 +2115,10 @@
         <v>15</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>18</v>
@@ -2135,20 +2126,20 @@
     </row>
     <row r="27" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="5">
         <v>3</v>
       </c>
       <c r="C27" s="6">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="D27" s="7"/>
-      <c r="E27" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>104</v>
+      <c r="E27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>31</v>
@@ -2157,10 +2148,10 @@
         <v>15</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>18</v>
@@ -2168,23 +2159,23 @@
     </row>
     <row r="28" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>3</v>
       </c>
       <c r="C28" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D28" s="7"/>
-      <c r="E28" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>31</v>
+      <c r="E28" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>15</v>
@@ -2207,26 +2198,26 @@
         <v>3</v>
       </c>
       <c r="C29" s="6">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>14</v>
+      <c r="E29" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J29" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>18</v>
@@ -2234,32 +2225,32 @@
     </row>
     <row r="30" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="5">
+        <v>3</v>
+      </c>
+      <c r="C30" s="6">
+        <v>30</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="5">
-        <v>3</v>
-      </c>
-      <c r="C30" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>31</v>
+      <c r="F30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>18</v>
@@ -2267,7 +2258,7 @@
     </row>
     <row r="31" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="5">
         <v>3</v>
@@ -2277,10 +2268,10 @@
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>13</v>
+        <v>114</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>101</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>14</v>
@@ -2310,10 +2301,10 @@
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>104</v>
+        <v>114</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>14</v>
@@ -2322,10 +2313,10 @@
         <v>15</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>122</v>
+        <v>220</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>18</v>
@@ -2333,20 +2324,20 @@
     </row>
     <row r="33" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B33" s="5">
         <v>3</v>
       </c>
       <c r="C33" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D33" s="7"/>
-      <c r="E33" s="23" t="s">
-        <v>117</v>
+      <c r="E33" s="19" t="s">
+        <v>55</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>14</v>
@@ -2355,10 +2346,10 @@
         <v>15</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>223</v>
+        <v>123</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>18</v>
@@ -2372,14 +2363,14 @@
         <v>3</v>
       </c>
       <c r="C34" s="6">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D34" s="7"/>
-      <c r="E34" s="19" t="s">
-        <v>58</v>
+      <c r="E34" s="23" t="s">
+        <v>114</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>14</v>
@@ -2408,11 +2399,11 @@
         <v>30</v>
       </c>
       <c r="D35" s="7"/>
-      <c r="E35" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>69</v>
+      <c r="E35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>14</v>
@@ -2441,8 +2432,8 @@
         <v>30</v>
       </c>
       <c r="D36" s="7"/>
-      <c r="E36" s="8" t="s">
-        <v>12</v>
+      <c r="E36" s="23" t="s">
+        <v>114</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>21</v>
@@ -2475,10 +2466,10 @@
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>21</v>
+        <v>114</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>14</v>
@@ -2487,10 +2478,10 @@
         <v>15</v>
       </c>
       <c r="I37" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="J37" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>135</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>18</v>
@@ -2498,20 +2489,20 @@
     </row>
     <row r="38" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B38" s="5">
         <v>3</v>
       </c>
       <c r="C38" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D38" s="7"/>
-      <c r="E38" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>13</v>
+      <c r="E38" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>14</v>
@@ -2540,14 +2531,14 @@
         <v>30.1</v>
       </c>
       <c r="D39" s="7"/>
-      <c r="E39" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>14</v>
+      <c r="E39" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>15</v>
@@ -2573,11 +2564,11 @@
         <v>30.1</v>
       </c>
       <c r="D40" s="7"/>
-      <c r="E40" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>104</v>
+      <c r="E40" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>31</v>
@@ -2603,14 +2594,14 @@
         <v>3</v>
       </c>
       <c r="C41" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D41" s="7"/>
-      <c r="E41" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>38</v>
+      <c r="E41" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>101</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>31</v>
@@ -2636,14 +2627,14 @@
         <v>3</v>
       </c>
       <c r="C42" s="6">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D42" s="7"/>
-      <c r="E42" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>104</v>
+      <c r="E42" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>31</v>
@@ -2652,10 +2643,10 @@
         <v>15</v>
       </c>
       <c r="I42" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="J42" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>149</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>18</v>
@@ -2663,20 +2654,20 @@
     </row>
     <row r="43" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B43" s="5">
         <v>3</v>
       </c>
       <c r="C43" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F43" s="17" t="s">
-        <v>38</v>
+      <c r="F43" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>31</v>
@@ -2685,7 +2676,7 @@
         <v>15</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>151</v>
@@ -2705,14 +2696,14 @@
         <v>30.1</v>
       </c>
       <c r="D44" s="7"/>
-      <c r="E44" s="9" t="s">
-        <v>30</v>
+      <c r="E44" s="16" t="s">
+        <v>42</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="16" t="s">
-        <v>31</v>
+      <c r="G44" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>15</v>
@@ -2735,14 +2726,14 @@
         <v>3</v>
       </c>
       <c r="C45" s="6">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>26</v>
+        <v>42</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>43</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>14</v>
@@ -2772,10 +2763,10 @@
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F46" s="18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>14</v>
@@ -2789,94 +2780,89 @@
       <c r="J46" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="K46" s="11" t="s">
-        <v>18</v>
+      <c r="K46" s="7" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G47" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B47" s="5">
-        <v>3</v>
-      </c>
-      <c r="C47" s="6">
-        <v>30.2</v>
-      </c>
-      <c r="D47" s="7"/>
-      <c r="E47" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>163</v>
-      </c>
+      <c r="H47" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
       <c r="K47" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C48" s="20"/>
+      <c r="B48" s="5">
+        <v>3</v>
+      </c>
+      <c r="C48" s="6">
+        <v>30.1</v>
+      </c>
       <c r="D48" s="7"/>
-      <c r="E48" s="18" t="s">
-        <v>166</v>
+      <c r="E48" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
       <c r="K48" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="20"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J49" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B49" s="5">
-        <v>3</v>
-      </c>
-      <c r="C49" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="D49" s="7"/>
-      <c r="E49" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="7" t="s">
-        <v>164</v>
+      <c r="K49" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2885,11 +2871,11 @@
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
+      <c r="E50" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>14</v>
@@ -2914,13 +2900,13 @@
       <c r="C51" s="20"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>14</v>
+        <v>70</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H51" s="11" t="s">
         <v>15</v>
@@ -2942,16 +2928,16 @@
       <c r="C52" s="20"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F52" s="23" t="s">
-        <v>104</v>
+        <v>70</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G52" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H52" s="11" t="s">
-        <v>15</v>
+      <c r="H52" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>176</v>
@@ -2959,8 +2945,8 @@
       <c r="J52" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="K52" s="11" t="s">
-        <v>18</v>
+      <c r="K52" s="7" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2970,16 +2956,16 @@
       <c r="C53" s="20"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>26</v>
+        <v>70</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>43</v>
       </c>
       <c r="G53" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H53" s="21" t="s">
-        <v>76</v>
+      <c r="H53" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>179</v>
@@ -2987,8 +2973,8 @@
       <c r="J53" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="K53" s="7" t="s">
-        <v>164</v>
+      <c r="K53" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2997,14 +2983,14 @@
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>31</v>
+      <c r="E54" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H54" s="11" t="s">
         <v>15</v>
@@ -3025,14 +3011,14 @@
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>14</v>
+      <c r="E55" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H55" s="11" t="s">
         <v>15</v>
@@ -3054,10 +3040,10 @@
       <c r="C56" s="20"/>
       <c r="D56" s="7"/>
       <c r="E56" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G56" s="16" t="s">
         <v>31</v>
@@ -3066,10 +3052,10 @@
         <v>15</v>
       </c>
       <c r="I56" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="J56" s="12" t="s">
         <v>188</v>
-      </c>
-      <c r="J56" s="12" t="s">
-        <v>189</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>18</v>
@@ -3077,15 +3063,15 @@
     </row>
     <row r="57" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C57" s="20"/>
       <c r="D57" s="7"/>
-      <c r="E57" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F57" s="16" t="s">
-        <v>74</v>
+      <c r="E57" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>31</v>
@@ -3094,10 +3080,10 @@
         <v>15</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>18</v>
@@ -3105,30 +3091,30 @@
     </row>
     <row r="58" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="7"/>
-      <c r="E58" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>31</v>
+      <c r="E58" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58" s="26" t="s">
+        <v>192</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>179</v>
+        <v>63</v>
       </c>
       <c r="J58" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="K58" s="11" t="s">
-        <v>18</v>
+      <c r="K58" s="7" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3138,25 +3124,25 @@
       <c r="C59" s="20"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F59" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="G59" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="K59" s="7" t="s">
-        <v>164</v>
+      <c r="K59" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3166,13 +3152,13 @@
       <c r="C60" s="20"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>14</v>
+        <v>70</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>15</v>
@@ -3193,14 +3179,14 @@
       </c>
       <c r="C61" s="20"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="7" t="s">
-        <v>73</v>
+      <c r="E61" s="18" t="s">
+        <v>163</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>31</v>
+        <v>43</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>15</v>
@@ -3219,25 +3205,32 @@
       <c r="A62" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C62" s="20"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>46</v>
+      <c r="B62" s="5">
+        <v>3</v>
+      </c>
+      <c r="C62" s="6">
+        <v>30</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="27" t="s">
+        <v>205</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H62" s="11" t="s">
-        <v>15</v>
+      <c r="H62" s="28" t="s">
+        <v>206</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>18</v>
@@ -3245,7 +3238,7 @@
     </row>
     <row r="63" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B63" s="5">
         <v>3</v>
@@ -3254,25 +3247,25 @@
         <v>30</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F63" s="27" t="s">
-        <v>208</v>
+      <c r="F63" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H63" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="I63" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="I63" s="12" t="s">
+      <c r="J63" s="12" t="s">
         <v>210</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>211</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>18</v>
@@ -3280,28 +3273,28 @@
     </row>
     <row r="64" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B64" s="5">
         <v>3</v>
       </c>
       <c r="C64" s="6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F64" s="24" t="s">
-        <v>108</v>
+      <c r="F64" s="18" t="s">
+        <v>43</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>212</v>
@@ -3321,22 +3314,22 @@
         <v>3</v>
       </c>
       <c r="C65" s="6">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F65" s="18" t="s">
-        <v>46</v>
+      <c r="F65" s="23" t="s">
+        <v>101</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H65" s="28" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>215</v>
@@ -3359,19 +3352,19 @@
         <v>30</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F66" s="23" t="s">
-        <v>104</v>
+      <c r="F66" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="28" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>218</v>
@@ -3383,42 +3376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B67" s="5">
-        <v>3</v>
-      </c>
-      <c r="C67" s="6">
-        <v>30</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="J67" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="K67" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucifer/vscode_Luci_scripts/HBCD-DOCS/2.1-dev/hbcd-docs/docs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A788107-24C6-994B-B1EF-5C12225B8D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66A354C-A769-1744-8742-E04DE03A11E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,9 +493,6 @@
     <t>QSIRecon</t>
   </si>
   <si>
-    <t>Tabulated data for QSIRecon (participant data combined across derivative files into single tidy table) will be provided in a future release.</t>
-  </si>
-  <si>
     <t>XCP-D corrections and model output</t>
   </si>
   <si>
@@ -683,6 +680,9 @@
   </si>
   <si>
     <t>Addition of V6 Adult and V6 Child Demographics</t>
+  </si>
+  <si>
+    <t>Addition of tabulated data for QSIRecon (participant data combined across derivative files into single tidy table).</t>
   </si>
 </sst>
 </file>
@@ -2316,7 +2316,7 @@
         <v>96</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>18</v>
@@ -2745,7 +2745,7 @@
         <v>156</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>18</v>
@@ -2753,7 +2753,7 @@
     </row>
     <row r="46" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B46" s="5">
         <v>3</v>
@@ -2775,42 +2775,42 @@
         <v>15</v>
       </c>
       <c r="I46" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J46" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="K46" s="7" t="s">
         <v>160</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="7"/>
       <c r="E47" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>164</v>
-      </c>
       <c r="G47" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="12"/>
       <c r="K47" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5">
         <v>3</v>
@@ -2823,23 +2823,23 @@
         <v>30</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
       <c r="K48" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C49" s="20"/>
       <c r="D49" s="7"/>
@@ -2856,10 +2856,10 @@
         <v>15</v>
       </c>
       <c r="I49" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="J49" s="12" t="s">
         <v>167</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>168</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>18</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="50" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="7"/>
@@ -2884,10 +2884,10 @@
         <v>15</v>
       </c>
       <c r="I50" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="J50" s="12" t="s">
         <v>170</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>171</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>18</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="51" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="7"/>
@@ -2912,10 +2912,10 @@
         <v>15</v>
       </c>
       <c r="I51" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="J51" s="12" t="s">
         <v>173</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>174</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>18</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="52" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C52" s="20"/>
       <c r="D52" s="7"/>
@@ -2940,18 +2940,18 @@
         <v>73</v>
       </c>
       <c r="I52" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J52" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="J52" s="12" t="s">
-        <v>177</v>
-      </c>
       <c r="K52" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="7"/>
@@ -2968,10 +2968,10 @@
         <v>15</v>
       </c>
       <c r="I53" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="J53" s="12" t="s">
         <v>179</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>180</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>18</v>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="54" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="7"/>
@@ -2996,10 +2996,10 @@
         <v>15</v>
       </c>
       <c r="I54" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J54" s="12" t="s">
         <v>182</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>183</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>18</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="55" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="7"/>
@@ -3024,10 +3024,10 @@
         <v>15</v>
       </c>
       <c r="I55" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="J55" s="12" t="s">
         <v>185</v>
-      </c>
-      <c r="J55" s="12" t="s">
-        <v>186</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>18</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="56" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C56" s="20"/>
       <c r="D56" s="7"/>
@@ -3052,10 +3052,10 @@
         <v>15</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>18</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="57" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C57" s="20"/>
       <c r="D57" s="7"/>
@@ -3080,10 +3080,10 @@
         <v>15</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>18</v>
@@ -3091,7 +3091,7 @@
     </row>
     <row r="58" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="7"/>
@@ -3102,7 +3102,7 @@
         <v>71</v>
       </c>
       <c r="G58" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>15</v>
@@ -3111,15 +3111,15 @@
         <v>63</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C59" s="20"/>
       <c r="D59" s="7"/>
@@ -3136,10 +3136,10 @@
         <v>15</v>
       </c>
       <c r="I59" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="J59" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>18</v>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="60" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="7"/>
@@ -3164,10 +3164,10 @@
         <v>15</v>
       </c>
       <c r="I60" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="J60" s="12" t="s">
         <v>198</v>
-      </c>
-      <c r="J60" s="12" t="s">
-        <v>199</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>18</v>
@@ -3175,12 +3175,12 @@
     </row>
     <row r="61" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C61" s="20"/>
       <c r="D61" s="7"/>
       <c r="E61" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>43</v>
@@ -3192,10 +3192,10 @@
         <v>15</v>
       </c>
       <c r="I61" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="J61" s="12" t="s">
         <v>201</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>202</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>18</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="62" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B62" s="5">
         <v>3</v>
@@ -3212,25 +3212,25 @@
         <v>30</v>
       </c>
       <c r="D62" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="27" t="s">
         <v>204</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="27" t="s">
-        <v>205</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="I62" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="J62" s="12" t="s">
         <v>207</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>208</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>18</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="63" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B63" s="5">
         <v>3</v>
@@ -3247,7 +3247,7 @@
         <v>30</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>15</v>
@@ -3259,13 +3259,13 @@
         <v>14</v>
       </c>
       <c r="H63" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I63" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="J63" s="12" t="s">
         <v>209</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>210</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>18</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="64" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>3</v>
@@ -3282,7 +3282,7 @@
         <v>30.1</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>15</v>
@@ -3294,13 +3294,13 @@
         <v>14</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I64" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J64" s="12" t="s">
         <v>212</v>
-      </c>
-      <c r="J64" s="12" t="s">
-        <v>213</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>18</v>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="65" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B65" s="5">
         <v>3</v>
@@ -3317,7 +3317,7 @@
         <v>30</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>15</v>
@@ -3329,13 +3329,13 @@
         <v>14</v>
       </c>
       <c r="H65" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I65" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J65" s="12" t="s">
         <v>215</v>
-      </c>
-      <c r="J65" s="12" t="s">
-        <v>216</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>18</v>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="66" spans="1:11" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>3</v>
@@ -3352,7 +3352,7 @@
         <v>30</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>15</v>
@@ -3364,13 +3364,13 @@
         <v>14</v>
       </c>
       <c r="H66" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I66" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="J66" s="12" t="s">
         <v>218</v>
-      </c>
-      <c r="J66" s="12" t="s">
-        <v>219</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>18</v>

--- a/docs/data/latest.xlsx
+++ b/docs/data/latest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10911"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51ACDC6A-62FB-D144-8757-8FEBEE87A6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5A3FFC-338A-7A4D-90B9-E8710F3B453A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="140">
   <si>
     <t>Name</t>
   </si>
@@ -260,66 +260,21 @@
     <t>Postprocessing</t>
   </si>
   <si>
-    <t>[DATA REQUESTs] - novel tech QC feedback overview</t>
-  </si>
-  <si>
     <t>Novel Tech &amp; Wearable Sensors</t>
   </si>
   <si>
-    <t>unsure</t>
-  </si>
-  <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>[DATA ERRORS]- static table QC feedback</t>
-  </si>
-  <si>
-    <t>UNSURE</t>
-  </si>
-  <si>
     <t>Add scanner info as tabulated data</t>
   </si>
   <si>
     <t>Scanner info</t>
   </si>
   <si>
-    <t>[DATA ERROR]- home 21</t>
-  </si>
-  <si>
-    <t>br_known_issue</t>
-  </si>
-  <si>
-    <t>Not done</t>
-  </si>
-  <si>
-    <t>HOME-21</t>
-  </si>
-  <si>
-    <t>Tabulated XCP-D derivatives all 0s for numeric fields</t>
-  </si>
-  <si>
-    <t>Tabulated XCP-D</t>
-  </si>
-  <si>
-    <t>[REMOVE INSTRUMENT]- incarceration questionnaire</t>
-  </si>
-  <si>
-    <t>br_pending</t>
-  </si>
-  <si>
     <t>Incarceration</t>
   </si>
   <si>
-    <t>[SCORING ERROR]- eHITS</t>
-  </si>
-  <si>
-    <t>[DATA ERROR]- substance use flags in dynamic table</t>
-  </si>
-  <si>
-    <t>[DATA UPDATE]- blank out implausible z scores in anthro data</t>
-  </si>
-  <si>
     <t>[DATA REQUEST]- revise formatting of vision screener files</t>
   </si>
   <si>
@@ -369,9 +324,6 @@
   </si>
   <si>
     <t>DD 'instruction' field all blank</t>
-  </si>
-  <si>
-    <t>8 PNR not administered V1 portion of TLFB</t>
   </si>
   <si>
     <t>Early Child Care and Education</t>
@@ -508,7 +460,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -582,16 +534,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF7575"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF6D3B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCAB641"/>
       </patternFill>
     </fill>
@@ -613,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -664,12 +606,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1011,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="73" customWidth="1"/>
@@ -1807,59 +1743,59 @@
     </row>
     <row r="35" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B35" s="3">
         <v>3</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="C35" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>84</v>
+      <c r="G35" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="3">
-        <v>3</v>
-      </c>
-      <c r="C36" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>84</v>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="3">
-        <v>3</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>27</v>
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>9</v>
@@ -1868,7 +1804,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>12</v>
@@ -1876,48 +1812,48 @@
     </row>
     <row r="38" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="16" t="s">
+      <c r="C38" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>84</v>
+      <c r="G38" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>93</v>
-      </c>
-      <c r="B39" s="3">
-        <v>3</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>12</v>
+      <c r="G39" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1927,17 +1863,17 @@
       <c r="B40" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="18" t="s">
+      <c r="C40" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>12</v>
@@ -1945,25 +1881,25 @@
     </row>
     <row r="41" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B41" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>91</v>
+      <c r="C41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>84</v>
+        <v>98</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1973,63 +1909,63 @@
       <c r="B42" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>84</v>
+      <c r="C42" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>84</v>
+        <v>100</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B43" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>84</v>
+      <c r="C43" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>84</v>
+        <v>100</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>9</v>
+      <c r="C44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>12</v>
@@ -2042,8 +1978,8 @@
       <c r="B45" t="s">
         <v>40</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>17</v>
+      <c r="C45" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>9</v>
@@ -2065,8 +2001,8 @@
       <c r="B46" t="s">
         <v>40</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>58</v>
+      <c r="C46" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>20</v>
@@ -2088,31 +2024,31 @@
       <c r="B47" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E47" s="11" t="s">
+      <c r="C47" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>84</v>
+      <c r="G47" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="C48" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="B48" t="s">
-        <v>40</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>27</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>20</v>
@@ -2131,20 +2067,20 @@
       <c r="A49" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B49" t="s">
-        <v>40</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>8</v>
+      <c r="B49" s="3">
+        <v>3</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>10</v>
+      <c r="E49" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>12</v>
@@ -2152,19 +2088,19 @@
     </row>
     <row r="50" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>10</v>
+        <v>115</v>
+      </c>
+      <c r="B50" s="3">
+        <v>3</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>115</v>
@@ -2177,20 +2113,20 @@
       <c r="A51" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B51" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>10</v>
+      <c r="B51" s="3">
+        <v>3</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>12</v>
@@ -2198,22 +2134,22 @@
     </row>
     <row r="52" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B52" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>10</v>
+        <v>118</v>
+      </c>
+      <c r="B52" s="3">
+        <v>3</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>12</v>
@@ -2221,45 +2157,45 @@
     </row>
     <row r="53" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B53" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>10</v>
+        <v>120</v>
+      </c>
+      <c r="B53" s="3">
+        <v>3</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>84</v>
+        <v>121</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B54" t="s">
-        <v>40</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>14</v>
+        <v>122</v>
+      </c>
+      <c r="B54" s="3">
+        <v>3</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>10</v>
+      <c r="E54" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>12</v>
@@ -2267,22 +2203,22 @@
     </row>
     <row r="55" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B55" t="s">
-        <v>40</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>10</v>
+        <v>124</v>
+      </c>
+      <c r="B55" s="3">
+        <v>3</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>12</v>
@@ -2290,22 +2226,22 @@
     </row>
     <row r="56" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B56" t="s">
-        <v>40</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>27</v>
+        <v>126</v>
+      </c>
+      <c r="B56" s="3">
+        <v>3</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>10</v>
+      <c r="E56" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>12</v>
@@ -2313,22 +2249,22 @@
     </row>
     <row r="57" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B57" s="3">
-        <v>3.1</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>12</v>
@@ -2336,22 +2272,22 @@
     </row>
     <row r="58" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" s="3">
         <v>3</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>82</v>
+      <c r="C58" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>12</v>
@@ -2359,22 +2295,22 @@
     </row>
     <row r="59" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B59" s="3">
         <v>3</v>
       </c>
-      <c r="C59" s="18" t="s">
-        <v>126</v>
+      <c r="C59" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="19" t="s">
-        <v>129</v>
+      <c r="E59" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>12</v>
@@ -2382,19 +2318,19 @@
     </row>
     <row r="60" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="3">
+        <v>3</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="B60" s="3">
-        <v>3</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>129</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>133</v>
@@ -2410,14 +2346,14 @@
       <c r="B61" s="3">
         <v>3</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>129</v>
+      <c r="C61" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>135</v>
@@ -2433,14 +2369,14 @@
       <c r="B62" s="3">
         <v>3</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>8</v>
+      <c r="C62" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="19" t="s">
-        <v>129</v>
+      <c r="E62" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>137</v>
@@ -2456,14 +2392,14 @@
       <c r="B63" s="3">
         <v>3</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>129</v>
+      <c r="C63" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>139</v>
@@ -2472,214 +2408,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B64" s="3">
-        <v>3</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B65" s="3">
-        <v>3</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B66" s="3">
-        <v>3</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B67" s="3">
-        <v>3</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B68" s="3">
-        <v>3</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B69" s="3">
-        <v>3</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B70" s="3">
-        <v>3</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B71" s="3">
-        <v>3</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B72" s="3">
-        <v>3</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
